--- a/presentation/간트차트.xlsx
+++ b/presentation/간트차트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Desktop\FlowCast\FlowCast\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB807DF-9431-4F38-9431-B1E9BA3EC81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE8989-298F-4B6E-8DEE-2846B6F188CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36120" yWindow="1035" windowWidth="19110" windowHeight="11910" xr2:uid="{053B4E68-EAAD-4DD4-9196-11B744C7B87D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{053B4E68-EAAD-4DD4-9196-11B744C7B87D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>활동내용</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,6 +131,26 @@
   </si>
   <si>
     <t>수행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박선우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정종혁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김도현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조명환</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -141,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,8 +186,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,6 +238,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -437,7 +495,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -507,9 +565,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -519,6 +574,42 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -528,40 +619,22 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -901,19 +974,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="26"/>
+    <col min="1" max="1" width="8.796875" style="25"/>
     <col min="2" max="2" width="38.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="14" width="15.8984375" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="15.8984375" customWidth="1"/>
-    <col min="17" max="17" width="4.296875" style="26" customWidth="1"/>
-    <col min="18" max="19" width="16.09765625" style="26" customWidth="1"/>
-    <col min="20" max="20" width="4.296875" style="26" customWidth="1"/>
+    <col min="17" max="17" width="4.296875" style="25" customWidth="1"/>
+    <col min="18" max="19" width="16.09765625" style="25" customWidth="1"/>
+    <col min="20" max="20" width="4.296875" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" s="26" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="1" spans="2:19" s="25" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:19" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -962,32 +1035,32 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="32"/>
-      <c r="R3" s="25" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="28"/>
+      <c r="R3" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="24" t="s">
+      <c r="S3" s="23" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="33" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="5"/>
@@ -1006,7 +1079,7 @@
       <c r="P4" s="8"/>
     </row>
     <row r="5" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -1023,7 +1096,7 @@
       <c r="P5" s="12"/>
     </row>
     <row r="6" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="35" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13"/>
@@ -1042,7 +1115,7 @@
       <c r="P6" s="12"/>
     </row>
     <row r="7" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="13"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1059,7 +1132,7 @@
       <c r="P7" s="12"/>
     </row>
     <row r="8" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="13"/>
@@ -1078,7 +1151,7 @@
       <c r="P8" s="12"/>
     </row>
     <row r="9" spans="2:19" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="37"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="15"/>
       <c r="D9" s="16"/>
       <c r="E9" s="17"/>
@@ -1095,26 +1168,26 @@
       <c r="P9" s="18"/>
     </row>
     <row r="10" spans="2:19" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="32"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="28"/>
     </row>
     <row r="11" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="37" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="19"/>
@@ -1133,7 +1206,7 @@
       <c r="P11" s="8"/>
     </row>
     <row r="12" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B12" s="39"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="13"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
@@ -1150,7 +1223,7 @@
       <c r="P12" s="12"/>
     </row>
     <row r="13" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="13"/>
@@ -1169,7 +1242,7 @@
       <c r="P13" s="12"/>
     </row>
     <row r="14" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B14" s="39"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="13"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
@@ -1186,7 +1259,7 @@
       <c r="P14" s="12"/>
     </row>
     <row r="15" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="13"/>
@@ -1205,7 +1278,7 @@
       <c r="P15" s="12"/>
     </row>
     <row r="16" spans="2:19" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B16" s="39"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="13"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -1222,7 +1295,7 @@
       <c r="P16" s="12"/>
     </row>
     <row r="17" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="30" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="13"/>
@@ -1241,7 +1314,7 @@
       <c r="P17" s="12"/>
     </row>
     <row r="18" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B18" s="39"/>
+      <c r="B18" s="31"/>
       <c r="C18" s="13"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
@@ -1258,7 +1331,7 @@
       <c r="P18" s="12"/>
     </row>
     <row r="19" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="30" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="13"/>
@@ -1277,7 +1350,7 @@
       <c r="P19" s="12"/>
     </row>
     <row r="20" spans="2:16" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="41"/>
+      <c r="B20" s="32"/>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
@@ -1294,26 +1367,26 @@
       <c r="P20" s="18"/>
     </row>
     <row r="21" spans="2:16" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="32"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="28"/>
     </row>
     <row r="22" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="19"/>
@@ -1332,7 +1405,7 @@
       <c r="P22" s="8"/>
     </row>
     <row r="23" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B23" s="35"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="13"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -1349,7 +1422,7 @@
       <c r="P23" s="12"/>
     </row>
     <row r="24" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="35" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="13"/>
@@ -1368,7 +1441,7 @@
       <c r="P24" s="12"/>
     </row>
     <row r="25" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B25" s="35"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="13"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
@@ -1385,7 +1458,7 @@
       <c r="P25" s="12"/>
     </row>
     <row r="26" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="13"/>
@@ -1404,7 +1477,7 @@
       <c r="P26" s="12"/>
     </row>
     <row r="27" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B27" s="35"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="13"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
@@ -1421,7 +1494,7 @@
       <c r="P27" s="12"/>
     </row>
     <row r="28" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="35" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="13"/>
@@ -1440,7 +1513,7 @@
       <c r="P28" s="12"/>
     </row>
     <row r="29" spans="2:16" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="37"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="15"/>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
@@ -1457,26 +1530,26 @@
       <c r="P29" s="18"/>
     </row>
     <row r="30" spans="2:16" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="32"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="28"/>
     </row>
     <row r="31" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="37" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="19"/>
@@ -1495,7 +1568,7 @@
       <c r="P31" s="8"/>
     </row>
     <row r="32" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B32" s="39"/>
+      <c r="B32" s="31"/>
       <c r="C32" s="13"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -1512,7 +1585,7 @@
       <c r="P32" s="12"/>
     </row>
     <row r="33" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="13"/>
@@ -1531,7 +1604,7 @@
       <c r="P33" s="20"/>
     </row>
     <row r="34" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B34" s="39"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="13"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -1548,7 +1621,7 @@
       <c r="P34" s="21"/>
     </row>
     <row r="35" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="13"/>
@@ -1567,7 +1640,7 @@
       <c r="P35" s="20"/>
     </row>
     <row r="36" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B36" s="39"/>
+      <c r="B36" s="31"/>
       <c r="C36" s="13"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -1584,7 +1657,7 @@
       <c r="P36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="13"/>
@@ -1603,7 +1676,7 @@
       <c r="P37" s="20"/>
     </row>
     <row r="38" spans="2:16" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="41"/>
+      <c r="B38" s="32"/>
       <c r="C38" s="15"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
@@ -1620,58 +1693,189 @@
       <c r="P38" s="22"/>
     </row>
     <row r="39" spans="2:16" ht="25.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="29"/>
-    </row>
-    <row r="40" spans="2:16" s="26" customFormat="1" ht="25.2" x14ac:dyDescent="0.4">
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+    </row>
+    <row r="40" spans="2:16" s="25" customFormat="1" ht="25.2" x14ac:dyDescent="0.4">
       <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-    </row>
-    <row r="41" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
+      <c r="C40" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="J40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40" s="45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" s="25" customFormat="1" ht="25.2" x14ac:dyDescent="0.4">
+      <c r="B41" s="11"/>
+      <c r="C41" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
+      <c r="M41" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="P41" s="43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" ht="25.2" x14ac:dyDescent="0.4">
+      <c r="B42" s="11"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="25"/>
+      <c r="P43" s="25"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="25"/>
+      <c r="P44" s="25"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B39:P39"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
     <mergeCell ref="B3:P3"/>
     <mergeCell ref="B10:P10"/>
     <mergeCell ref="B21:P21"/>
@@ -1688,11 +1892,6 @@
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B39:P39"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
